--- a/Archived_HE_Data/hedata_2026-08-07.xlsx
+++ b/Archived_HE_Data/hedata_2026-08-07.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F264"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -7883,6 +7883,156 @@
         <v>46241</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Dining Services Assistant</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F259" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Learning Center Instructor</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F260" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Library Associate</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F261" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Director of Institutional Advancement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F262" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Part-Time Clinical Resource Registered Nurse (CRRN)</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F263" s="2">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Adjunct Faculty Opportunities</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Miles City</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Miles Community College</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.milescc.edu/employment/</t>
+        </is>
+      </c>
+      <c r="F264" s="2">
+        <v>46241</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
